--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,58</t>
+          <t>-1,5; 8,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 8,08</t>
+          <t>-3,73; 8,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,81</t>
+          <t>-6,55; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 5,06</t>
+          <t>-7,13; 5,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 50,53</t>
+          <t>-6,3; 44,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 16,37</t>
+          <t>-6,71; 16,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 12,86</t>
+          <t>-12,62; 13,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 23,14</t>
+          <t>-27,62; 23,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 7,8</t>
+          <t>-1,3; 7,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,46</t>
+          <t>-3,17; 6,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 10,34</t>
+          <t>0,56; 10,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,45</t>
+          <t>2,8; 12,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 39,27</t>
+          <t>-5,29; 37,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 12,62</t>
+          <t>-5,5; 12,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 25,21</t>
+          <t>0,99; 26,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 54,07</t>
+          <t>9,94; 55,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 9,45</t>
+          <t>-0,85; 9,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 7,9</t>
+          <t>-2,83; 8,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 12,27</t>
+          <t>1,33; 12,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 52,23</t>
+          <t>-1,31; 51,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 51,33</t>
+          <t>-3,47; 53,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 14,99</t>
+          <t>-4,73; 16,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 39,42</t>
+          <t>3,45; 41,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 276,34</t>
+          <t>-5,65; 282,53</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,45</t>
+          <t>1,57; 10,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,0</t>
+          <t>-1,48; 8,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 12,74</t>
+          <t>2,73; 12,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 6,45</t>
+          <t>-5,29; 6,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 55,3</t>
+          <t>6,45; 52,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 19,14</t>
+          <t>-3,22; 20,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,41; 33,78</t>
+          <t>6,31; 33,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 34,45</t>
+          <t>-20,85; 34,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,7</t>
+          <t>1,95; 6,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,85</t>
+          <t>-0,45; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,92</t>
+          <t>2,47; 7,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 23,77</t>
+          <t>1,97; 24,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 32,93</t>
+          <t>8,87; 31,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 9,61</t>
+          <t>-0,85; 9,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,56</t>
+          <t>5,59; 19,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,39; 103,65</t>
+          <t>8,46; 113,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,49</t>
+          <t>-2,15; 8,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 8,13</t>
+          <t>-3,82; 8,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,11</t>
+          <t>-5,63; 6,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 5,25</t>
+          <t>-2,73; 7,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 44,5</t>
+          <t>-8,71; 41,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 16,23</t>
+          <t>-7,06; 16,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 13,37</t>
+          <t>-11,08; 14,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 23,54</t>
+          <t>-10,13; 34,01</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,81</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 7,47</t>
+          <t>-1,35; 7,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 6,62</t>
+          <t>-3,24; 6,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 10,91</t>
+          <t>0,96; 10,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,53</t>
+          <t>0,95; 9,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 37,26</t>
+          <t>-6,57; 37,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 12,66</t>
+          <t>-5,55; 13,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 26,73</t>
+          <t>1,84; 25,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,94; 55,09</t>
+          <t>2,68; 37,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,72</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,88</t>
+          <t>-0,79; 8,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 8,66</t>
+          <t>-2,45; 9,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 12,96</t>
+          <t>1,07; 12,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 51,92</t>
+          <t>-2,85; 7,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 53,38</t>
+          <t>-3,55; 48,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 16,99</t>
+          <t>-4,24; 17,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 41,04</t>
+          <t>2,65; 41,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 282,53</t>
+          <t>-11,27; 36,41</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>4,46</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 10,07</t>
+          <t>1,87; 10,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,77</t>
+          <t>-1,2; 8,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 12,34</t>
+          <t>2,24; 12,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,15</t>
+          <t>0,18; 8,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 52,55</t>
+          <t>7,51; 55,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 20,79</t>
+          <t>-2,73; 19,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 33,45</t>
+          <t>5,26; 32,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 34,83</t>
+          <t>0,65; 43,92</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,62</t>
+          <t>2,08; 6,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,92</t>
+          <t>-0,35; 5,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,85</t>
+          <t>2,85; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 24,73</t>
+          <t>1,19; 5,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 31,64</t>
+          <t>8,81; 32,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 9,75</t>
+          <t>-0,67; 9,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,59; 19,51</t>
+          <t>6,59; 20,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,46; 113,11</t>
+          <t>4,49; 25,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
